--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:59</t>
+    <t xml:space="preserve">2026-09-09 22:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:50</t>
+    <t xml:space="preserve">2026-09-18 10:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:12</t>
+    <t xml:space="preserve">2026-09-23 12:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:16</t>
+    <t xml:space="preserve">2026-10-02 13:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:49</t>
+    <t xml:space="preserve">2026-10-05 09:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
